--- a/completed/polyaromatic_synthesis_10.1039.c9ra04921e.xlsx
+++ b/completed/polyaromatic_synthesis_10.1039.c9ra04921e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/completed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E981FF-6495-0B43-9D38-C817B1614F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250697E5-B484-BC41-8CB9-C08AE1264061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="48">
   <si>
     <t>REACTION</t>
   </si>
@@ -74,9 +74,6 @@
     <t>DATA</t>
   </si>
   <si>
-    <t>Publication URL</t>
-  </si>
-  <si>
     <t>Duration (s)</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>City</t>
   </si>
   <si>
-    <t>TEMPTERATURE</t>
-  </si>
-  <si>
     <t>Temperature (Celsius)</t>
   </si>
   <si>
@@ -111,9 +105,6 @@
   </si>
   <si>
     <t>10.1039/c9ra04921e</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1039/C9RA04921E</t>
   </si>
   <si>
     <t>O=C(OCC)C1=CC2=CC=CC=C2C=C1C(OCC)=O</t>
@@ -169,20 +160,6 @@
     <t>O=CC1=CCCC=C1C=O</t>
   </si>
   <si>
-    <r>
-      <t>NaBH</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
     <t>LiCl</t>
   </si>
   <si>
@@ -220,6 +197,27 @@
   </si>
   <si>
     <t>Thermocouple Internal</t>
+  </si>
+  <si>
+    <t>TEMPERATURE</t>
+  </si>
+  <si>
+    <t>[Na+].[BH4-]</t>
+  </si>
+  <si>
+    <t>Record Created</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Yeu-Shiuan Ho</t>
+  </si>
+  <si>
+    <t>yeushiuanho@tamu.edu</t>
   </si>
 </sst>
 </file>
@@ -842,13 +840,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -856,25 +854,33 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5"/>
+      <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>47</v>
+      </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5"/>
@@ -919,7 +925,7 @@
       <c r="O7" s="1"/>
       <c r="P7" s="4"/>
       <c r="Q7" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -928,25 +934,25 @@
         <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="H8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>9</v>
@@ -958,22 +964,22 @@
         <v>4</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="s">
         <v>4</v>
       </c>
       <c r="R8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="9" customFormat="1" x14ac:dyDescent="0.2">
@@ -999,46 +1005,46 @@
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="6">
         <v>6</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E10" s="6">
         <v>13</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G10" s="6">
         <v>26</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I10" s="6">
         <v>5</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K10" s="6">
         <v>84</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M10">
         <v>18</v>
       </c>
       <c r="N10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P10" s="6">
         <f>20*60*60</f>
@@ -1048,19 +1054,19 @@
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="6">
         <v>3</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E11" s="6">
         <v>12</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G11" s="6">
         <v>30</v>
@@ -1068,22 +1074,22 @@
       <c r="H11" s="5"/>
       <c r="I11" s="6"/>
       <c r="J11" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K11" s="6">
         <v>75</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M11">
         <v>18</v>
       </c>
       <c r="N11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P11" s="6">
         <f>16*60*60</f>
@@ -1093,13 +1099,13 @@
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C12" s="6">
         <v>1.8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6">
         <v>5.4</v>
@@ -1109,22 +1115,22 @@
       <c r="H12" s="5"/>
       <c r="I12" s="6"/>
       <c r="J12" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K12" s="6">
         <v>81</v>
       </c>
       <c r="L12" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M12">
         <v>18</v>
       </c>
       <c r="N12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P12" s="6">
         <f>8*60*60</f>
@@ -1134,46 +1140,46 @@
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C13" s="6">
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E13" s="6">
         <v>6.5</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G13" s="6">
         <v>13</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I13" s="6">
         <v>2.5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K13" s="6">
         <v>62</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M13">
         <v>18</v>
       </c>
       <c r="N13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P13" s="6">
         <f>20*60*60</f>
@@ -1183,19 +1189,19 @@
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C14" s="21">
         <v>1</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E14" s="21">
         <v>4</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G14" s="21">
         <v>10</v>
@@ -1203,22 +1209,22 @@
       <c r="H14" s="5"/>
       <c r="I14" s="21"/>
       <c r="J14" s="22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K14" s="21">
         <v>55</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M14">
         <v>18</v>
       </c>
       <c r="N14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P14" s="6">
         <f>16*60*60</f>
@@ -1228,13 +1234,13 @@
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="15"/>
       <c r="B15" s="22" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C15" s="21">
         <v>1</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E15" s="21">
         <v>3</v>
@@ -1244,22 +1250,22 @@
       <c r="H15" s="5"/>
       <c r="I15" s="21"/>
       <c r="J15" s="22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K15" s="21">
         <v>81</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M15">
         <v>18</v>
       </c>
       <c r="N15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P15" s="6">
         <f>8*60*60</f>
@@ -1269,53 +1275,53 @@
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" s="21">
         <v>0.6</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E16" s="21">
         <v>1.3</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G16" s="21">
         <v>2.6</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I16" s="21">
         <v>0.6</v>
       </c>
       <c r="J16" s="22" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K16" s="21">
         <v>20</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M16">
         <v>18</v>
       </c>
       <c r="N16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P16" s="6">
         <f>12*60*60</f>
         <v>43200</v>
       </c>
       <c r="Q16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="R16">
         <v>80</v>
@@ -2059,7 +2065,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{D61F6307-70E1-9345-99E3-6D9748B989FE}"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{2D59C41E-D955-7247-9ED9-A4781CEB5784}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
